--- a/VM2026_Tipping_RuneH.xlsx
+++ b/VM2026_Tipping_RuneH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://consafelogistics-my.sharepoint.com/personal/martin_skaug_consafelogistics_com/Documents/Desktop/VM/Tipping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="8_{BA532E24-4EB7-4929-9C9D-50B3F9842F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4BE0D8E-1B54-48D8-BBA4-ED5B3197D8DF}"/>
+  <xr:revisionPtr revIDLastSave="252" documentId="8_{BA532E24-4EB7-4929-9C9D-50B3F9842F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{631FA673-1532-45DE-91A8-EDA811ADB4FC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1498,6 +1498,42 @@
     <xf numFmtId="0" fontId="14" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1512,42 +1548,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2110,111 +2110,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="M1" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="M1" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
     </row>
     <row r="2" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="56" t="s">
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="M2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="M2" s="69" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+      <c r="U2" s="69"/>
     </row>
     <row r="3" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="M3" s="59" t="s">
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="M3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
     </row>
     <row r="4" spans="1:32" ht="4.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="M5" s="61" t="s">
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="M5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="61"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="57"/>
     </row>
     <row r="6" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -2787,30 +2787,30 @@
       </c>
     </row>
     <row r="13" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="M13" s="61" t="s">
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="M13" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="N13" s="61"/>
-      <c r="O13" s="61"/>
-      <c r="P13" s="61"/>
-      <c r="Q13" s="61"/>
-      <c r="R13" s="61"/>
-      <c r="S13" s="61"/>
-      <c r="T13" s="61"/>
-      <c r="U13" s="61"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="57"/>
+      <c r="P13" s="57"/>
+      <c r="Q13" s="57"/>
+      <c r="R13" s="57"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="57"/>
+      <c r="U13" s="57"/>
     </row>
     <row r="14" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -3383,30 +3383,30 @@
       </c>
     </row>
     <row r="21" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="60"/>
-      <c r="M21" s="61" t="s">
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
+      <c r="M21" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="N21" s="61"/>
-      <c r="O21" s="61"/>
-      <c r="P21" s="61"/>
-      <c r="Q21" s="61"/>
-      <c r="R21" s="61"/>
-      <c r="S21" s="61"/>
-      <c r="T21" s="61"/>
-      <c r="U21" s="61"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="57"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="57"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="57"/>
     </row>
     <row r="22" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -3979,30 +3979,30 @@
       </c>
     </row>
     <row r="29" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="60" t="s">
+      <c r="A29" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="60"/>
-      <c r="C29" s="60"/>
-      <c r="D29" s="60"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="60"/>
-      <c r="J29" s="60"/>
-      <c r="K29" s="60"/>
-      <c r="M29" s="61" t="s">
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="56"/>
+      <c r="M29" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="N29" s="61"/>
-      <c r="O29" s="61"/>
-      <c r="P29" s="61"/>
-      <c r="Q29" s="61"/>
-      <c r="R29" s="61"/>
-      <c r="S29" s="61"/>
-      <c r="T29" s="61"/>
-      <c r="U29" s="61"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="57"/>
+      <c r="Q29" s="57"/>
+      <c r="R29" s="57"/>
+      <c r="S29" s="57"/>
+      <c r="T29" s="57"/>
+      <c r="U29" s="57"/>
     </row>
     <row r="30" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
@@ -4575,30 +4575,30 @@
       </c>
     </row>
     <row r="37" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="60" t="s">
+      <c r="A37" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="60"/>
-      <c r="C37" s="60"/>
-      <c r="D37" s="60"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="60"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="60"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="60"/>
-      <c r="M37" s="61" t="s">
+      <c r="B37" s="56"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="56"/>
+      <c r="M37" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="N37" s="61"/>
-      <c r="O37" s="61"/>
-      <c r="P37" s="61"/>
-      <c r="Q37" s="61"/>
-      <c r="R37" s="61"/>
-      <c r="S37" s="61"/>
-      <c r="T37" s="61"/>
-      <c r="U37" s="61"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="57"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
     </row>
     <row r="38" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
@@ -5171,30 +5171,30 @@
       </c>
     </row>
     <row r="45" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="60" t="s">
+      <c r="A45" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="60"/>
-      <c r="F45" s="60"/>
-      <c r="G45" s="60"/>
-      <c r="H45" s="60"/>
-      <c r="I45" s="60"/>
-      <c r="J45" s="60"/>
-      <c r="K45" s="60"/>
-      <c r="M45" s="61" t="s">
+      <c r="B45" s="56"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="56"/>
+      <c r="K45" s="56"/>
+      <c r="M45" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="N45" s="61"/>
-      <c r="O45" s="61"/>
-      <c r="P45" s="61"/>
-      <c r="Q45" s="61"/>
-      <c r="R45" s="61"/>
-      <c r="S45" s="61"/>
-      <c r="T45" s="61"/>
-      <c r="U45" s="61"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="57"/>
+      <c r="P45" s="57"/>
+      <c r="Q45" s="57"/>
+      <c r="R45" s="57"/>
+      <c r="S45" s="57"/>
+      <c r="T45" s="57"/>
+      <c r="U45" s="57"/>
     </row>
     <row r="46" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -5767,30 +5767,30 @@
       </c>
     </row>
     <row r="53" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="60" t="s">
+      <c r="A53" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="60"/>
-      <c r="C53" s="60"/>
-      <c r="D53" s="60"/>
-      <c r="E53" s="60"/>
-      <c r="F53" s="60"/>
-      <c r="G53" s="60"/>
-      <c r="H53" s="60"/>
-      <c r="I53" s="60"/>
-      <c r="J53" s="60"/>
-      <c r="K53" s="60"/>
-      <c r="M53" s="61" t="s">
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="56"/>
+      <c r="K53" s="56"/>
+      <c r="M53" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="N53" s="61"/>
-      <c r="O53" s="61"/>
-      <c r="P53" s="61"/>
-      <c r="Q53" s="61"/>
-      <c r="R53" s="61"/>
-      <c r="S53" s="61"/>
-      <c r="T53" s="61"/>
-      <c r="U53" s="61"/>
+      <c r="N53" s="57"/>
+      <c r="O53" s="57"/>
+      <c r="P53" s="57"/>
+      <c r="Q53" s="57"/>
+      <c r="R53" s="57"/>
+      <c r="S53" s="57"/>
+      <c r="T53" s="57"/>
+      <c r="U53" s="57"/>
     </row>
     <row r="54" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
@@ -6363,30 +6363,30 @@
       </c>
     </row>
     <row r="61" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="60" t="s">
+      <c r="A61" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="B61" s="60"/>
-      <c r="C61" s="60"/>
-      <c r="D61" s="60"/>
-      <c r="E61" s="60"/>
-      <c r="F61" s="60"/>
-      <c r="G61" s="60"/>
-      <c r="H61" s="60"/>
-      <c r="I61" s="60"/>
-      <c r="J61" s="60"/>
-      <c r="K61" s="60"/>
-      <c r="M61" s="61" t="s">
+      <c r="B61" s="56"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="56"/>
+      <c r="K61" s="56"/>
+      <c r="M61" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="N61" s="61"/>
-      <c r="O61" s="61"/>
-      <c r="P61" s="61"/>
-      <c r="Q61" s="61"/>
-      <c r="R61" s="61"/>
-      <c r="S61" s="61"/>
-      <c r="T61" s="61"/>
-      <c r="U61" s="61"/>
+      <c r="N61" s="57"/>
+      <c r="O61" s="57"/>
+      <c r="P61" s="57"/>
+      <c r="Q61" s="57"/>
+      <c r="R61" s="57"/>
+      <c r="S61" s="57"/>
+      <c r="T61" s="57"/>
+      <c r="U61" s="57"/>
     </row>
     <row r="62" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
@@ -6959,30 +6959,30 @@
       </c>
     </row>
     <row r="69" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="62" t="s">
+      <c r="A69" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="B69" s="62"/>
-      <c r="C69" s="62"/>
-      <c r="D69" s="62"/>
-      <c r="E69" s="62"/>
-      <c r="F69" s="62"/>
-      <c r="G69" s="62"/>
-      <c r="H69" s="62"/>
-      <c r="I69" s="62"/>
-      <c r="J69" s="62"/>
-      <c r="K69" s="62"/>
-      <c r="M69" s="63" t="s">
+      <c r="B69" s="61"/>
+      <c r="C69" s="61"/>
+      <c r="D69" s="61"/>
+      <c r="E69" s="61"/>
+      <c r="F69" s="61"/>
+      <c r="G69" s="61"/>
+      <c r="H69" s="61"/>
+      <c r="I69" s="61"/>
+      <c r="J69" s="61"/>
+      <c r="K69" s="61"/>
+      <c r="M69" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="N69" s="63"/>
-      <c r="O69" s="63"/>
-      <c r="P69" s="63"/>
-      <c r="Q69" s="63"/>
-      <c r="R69" s="63"/>
-      <c r="S69" s="63"/>
-      <c r="T69" s="63"/>
-      <c r="U69" s="63"/>
+      <c r="N69" s="62"/>
+      <c r="O69" s="62"/>
+      <c r="P69" s="62"/>
+      <c r="Q69" s="62"/>
+      <c r="R69" s="62"/>
+      <c r="S69" s="62"/>
+      <c r="T69" s="62"/>
+      <c r="U69" s="62"/>
     </row>
     <row r="70" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
@@ -7555,30 +7555,30 @@
       </c>
     </row>
     <row r="77" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="60" t="s">
+      <c r="A77" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="B77" s="60"/>
-      <c r="C77" s="60"/>
-      <c r="D77" s="60"/>
-      <c r="E77" s="60"/>
-      <c r="F77" s="60"/>
-      <c r="G77" s="60"/>
-      <c r="H77" s="60"/>
-      <c r="I77" s="60"/>
-      <c r="J77" s="60"/>
-      <c r="K77" s="60"/>
-      <c r="M77" s="61" t="s">
+      <c r="B77" s="56"/>
+      <c r="C77" s="56"/>
+      <c r="D77" s="56"/>
+      <c r="E77" s="56"/>
+      <c r="F77" s="56"/>
+      <c r="G77" s="56"/>
+      <c r="H77" s="56"/>
+      <c r="I77" s="56"/>
+      <c r="J77" s="56"/>
+      <c r="K77" s="56"/>
+      <c r="M77" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="N77" s="61"/>
-      <c r="O77" s="61"/>
-      <c r="P77" s="61"/>
-      <c r="Q77" s="61"/>
-      <c r="R77" s="61"/>
-      <c r="S77" s="61"/>
-      <c r="T77" s="61"/>
-      <c r="U77" s="61"/>
+      <c r="N77" s="57"/>
+      <c r="O77" s="57"/>
+      <c r="P77" s="57"/>
+      <c r="Q77" s="57"/>
+      <c r="R77" s="57"/>
+      <c r="S77" s="57"/>
+      <c r="T77" s="57"/>
+      <c r="U77" s="57"/>
     </row>
     <row r="78" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
@@ -8151,30 +8151,30 @@
       </c>
     </row>
     <row r="85" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="60" t="s">
+      <c r="A85" s="56" t="s">
         <v>143</v>
       </c>
-      <c r="B85" s="60"/>
-      <c r="C85" s="60"/>
-      <c r="D85" s="60"/>
-      <c r="E85" s="60"/>
-      <c r="F85" s="60"/>
-      <c r="G85" s="60"/>
-      <c r="H85" s="60"/>
-      <c r="I85" s="60"/>
-      <c r="J85" s="60"/>
-      <c r="K85" s="60"/>
-      <c r="M85" s="61" t="s">
+      <c r="B85" s="56"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="56"/>
+      <c r="E85" s="56"/>
+      <c r="F85" s="56"/>
+      <c r="G85" s="56"/>
+      <c r="H85" s="56"/>
+      <c r="I85" s="56"/>
+      <c r="J85" s="56"/>
+      <c r="K85" s="56"/>
+      <c r="M85" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="N85" s="61"/>
-      <c r="O85" s="61"/>
-      <c r="P85" s="61"/>
-      <c r="Q85" s="61"/>
-      <c r="R85" s="61"/>
-      <c r="S85" s="61"/>
-      <c r="T85" s="61"/>
-      <c r="U85" s="61"/>
+      <c r="N85" s="57"/>
+      <c r="O85" s="57"/>
+      <c r="P85" s="57"/>
+      <c r="Q85" s="57"/>
+      <c r="R85" s="57"/>
+      <c r="S85" s="57"/>
+      <c r="T85" s="57"/>
+      <c r="U85" s="57"/>
     </row>
     <row r="86" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
@@ -8747,30 +8747,30 @@
       </c>
     </row>
     <row r="93" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="60" t="s">
+      <c r="A93" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="B93" s="60"/>
-      <c r="C93" s="60"/>
-      <c r="D93" s="60"/>
-      <c r="E93" s="60"/>
-      <c r="F93" s="60"/>
-      <c r="G93" s="60"/>
-      <c r="H93" s="60"/>
-      <c r="I93" s="60"/>
-      <c r="J93" s="60"/>
-      <c r="K93" s="60"/>
-      <c r="M93" s="61" t="s">
+      <c r="B93" s="56"/>
+      <c r="C93" s="56"/>
+      <c r="D93" s="56"/>
+      <c r="E93" s="56"/>
+      <c r="F93" s="56"/>
+      <c r="G93" s="56"/>
+      <c r="H93" s="56"/>
+      <c r="I93" s="56"/>
+      <c r="J93" s="56"/>
+      <c r="K93" s="56"/>
+      <c r="M93" s="57" t="s">
         <v>152</v>
       </c>
-      <c r="N93" s="61"/>
-      <c r="O93" s="61"/>
-      <c r="P93" s="61"/>
-      <c r="Q93" s="61"/>
-      <c r="R93" s="61"/>
-      <c r="S93" s="61"/>
-      <c r="T93" s="61"/>
-      <c r="U93" s="61"/>
+      <c r="N93" s="57"/>
+      <c r="O93" s="57"/>
+      <c r="P93" s="57"/>
+      <c r="Q93" s="57"/>
+      <c r="R93" s="57"/>
+      <c r="S93" s="57"/>
+      <c r="T93" s="57"/>
+      <c r="U93" s="57"/>
     </row>
     <row r="94" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
@@ -9350,12 +9350,12 @@
       <c r="E101" s="12"/>
       <c r="F101" s="12"/>
       <c r="G101" s="12"/>
-      <c r="H101" s="67" t="s">
+      <c r="H101" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="I101" s="67"/>
-      <c r="J101" s="67"/>
-      <c r="K101" s="67"/>
+      <c r="I101" s="58"/>
+      <c r="J101" s="58"/>
+      <c r="K101" s="58"/>
       <c r="L101" s="12"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12"/>
@@ -9421,11 +9421,11 @@
       <c r="F103" s="12"/>
       <c r="G103" s="12"/>
       <c r="H103" s="14"/>
-      <c r="I103" s="68" t="s">
+      <c r="I103" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="J103" s="68"/>
-      <c r="K103" s="68"/>
+      <c r="J103" s="59"/>
+      <c r="K103" s="59"/>
       <c r="L103" s="12"/>
       <c r="M103" s="12"/>
       <c r="N103" s="12"/>
@@ -9457,7 +9457,7 @@
       <c r="G104" s="12"/>
       <c r="H104" s="15" t="str">
         <f>COUNTIF(H105:H136,1)&amp;"/16"</f>
-        <v>0/16</v>
+        <v>16/16</v>
       </c>
       <c r="I104" s="16" t="s">
         <v>18</v>
@@ -9493,7 +9493,9 @@
       <c r="E105" s="12"/>
       <c r="F105" s="12"/>
       <c r="G105" s="12"/>
-      <c r="H105" s="18"/>
+      <c r="H105" s="18">
+        <v>1</v>
+      </c>
       <c r="I105" s="19" t="str">
         <f>IFERROR(M7,"A1")</f>
         <v>Tsjekkia</v>
@@ -9531,7 +9533,9 @@
       <c r="E106" s="12"/>
       <c r="F106" s="12"/>
       <c r="G106" s="12"/>
-      <c r="H106" s="21"/>
+      <c r="H106" s="21">
+        <v>1</v>
+      </c>
       <c r="I106" s="22" t="str">
         <f>IFERROR(M8,"A2")</f>
         <v>Mexico</v>
@@ -9647,7 +9651,9 @@
       <c r="E109" s="12"/>
       <c r="F109" s="12"/>
       <c r="G109" s="12"/>
-      <c r="H109" s="18"/>
+      <c r="H109" s="18">
+        <v>1</v>
+      </c>
       <c r="I109" s="19" t="str">
         <f>IFERROR(M23,"C1")</f>
         <v>Brasil</v>
@@ -9685,7 +9691,9 @@
       <c r="E110" s="12"/>
       <c r="F110" s="12"/>
       <c r="G110" s="12"/>
-      <c r="H110" s="21"/>
+      <c r="H110" s="21">
+        <v>1</v>
+      </c>
       <c r="I110" s="22" t="str">
         <f>IFERROR(M24,"C2")</f>
         <v>Marokko</v>
@@ -9723,7 +9731,9 @@
       <c r="E111" s="12"/>
       <c r="F111" s="12"/>
       <c r="G111" s="12"/>
-      <c r="H111" s="18"/>
+      <c r="H111" s="18">
+        <v>1</v>
+      </c>
       <c r="I111" s="19" t="str">
         <f>IFERROR(M31,"D1")</f>
         <v>USA</v>
@@ -9800,7 +9810,9 @@
       <c r="E113" s="12"/>
       <c r="F113" s="12"/>
       <c r="G113" s="12"/>
-      <c r="H113" s="18"/>
+      <c r="H113" s="18">
+        <v>1</v>
+      </c>
       <c r="I113" s="19" t="str">
         <f>IFERROR(M39,"E1")</f>
         <v>Tyskland</v>
@@ -9877,7 +9889,9 @@
       <c r="E115" s="12"/>
       <c r="F115" s="12"/>
       <c r="G115" s="12"/>
-      <c r="H115" s="18"/>
+      <c r="H115" s="18">
+        <v>1</v>
+      </c>
       <c r="I115" s="19" t="str">
         <f>IFERROR(M47,"F1")</f>
         <v>Nederland</v>
@@ -9954,7 +9968,9 @@
       <c r="E117" s="12"/>
       <c r="F117" s="12"/>
       <c r="G117" s="12"/>
-      <c r="H117" s="18"/>
+      <c r="H117" s="18">
+        <v>1</v>
+      </c>
       <c r="I117" s="19" t="str">
         <f>IFERROR(M55,"G1")</f>
         <v>Belgia</v>
@@ -10031,7 +10047,9 @@
       <c r="E119" s="12"/>
       <c r="F119" s="12"/>
       <c r="G119" s="12"/>
-      <c r="H119" s="18"/>
+      <c r="H119" s="18">
+        <v>1</v>
+      </c>
       <c r="I119" s="19" t="str">
         <f>IFERROR(M63,"H1")</f>
         <v>Spania</v>
@@ -10108,7 +10126,9 @@
       <c r="E121" s="12"/>
       <c r="F121" s="12"/>
       <c r="G121" s="12"/>
-      <c r="H121" s="18"/>
+      <c r="H121" s="18">
+        <v>1</v>
+      </c>
       <c r="I121" s="19" t="str">
         <f>IFERROR(M71,"I1")</f>
         <v>Frankrike</v>
@@ -10146,7 +10166,9 @@
       <c r="E122" s="12"/>
       <c r="F122" s="12"/>
       <c r="G122" s="12"/>
-      <c r="H122" s="21"/>
+      <c r="H122" s="21">
+        <v>1</v>
+      </c>
       <c r="I122" s="22" t="str">
         <f>IFERROR(M72,"I2")</f>
         <v>Norge</v>
@@ -10184,7 +10206,9 @@
       <c r="E123" s="12"/>
       <c r="F123" s="12"/>
       <c r="G123" s="12"/>
-      <c r="H123" s="18"/>
+      <c r="H123" s="18">
+        <v>1</v>
+      </c>
       <c r="I123" s="19" t="str">
         <f>IFERROR(M79,"J1")</f>
         <v>Argentina</v>
@@ -10261,7 +10285,9 @@
       <c r="E125" s="12"/>
       <c r="F125" s="12"/>
       <c r="G125" s="12"/>
-      <c r="H125" s="18"/>
+      <c r="H125" s="18">
+        <v>1</v>
+      </c>
       <c r="I125" s="19" t="str">
         <f>IFERROR(M87,"K1")</f>
         <v>Portugal</v>
@@ -10338,7 +10364,9 @@
       <c r="E127" s="12"/>
       <c r="F127" s="12"/>
       <c r="G127" s="12"/>
-      <c r="H127" s="18"/>
+      <c r="H127" s="18">
+        <v>1</v>
+      </c>
       <c r="I127" s="19" t="str">
         <f>IFERROR(M95,"L1")</f>
         <v>England</v>
@@ -10376,7 +10404,9 @@
       <c r="E128" s="12"/>
       <c r="F128" s="12"/>
       <c r="G128" s="12"/>
-      <c r="H128" s="21"/>
+      <c r="H128" s="21">
+        <v>1</v>
+      </c>
       <c r="I128" s="22" t="str">
         <f>IFERROR(M96,"L2")</f>
         <v>Kroatia</v>
@@ -10453,7 +10483,9 @@
       <c r="E130" s="12"/>
       <c r="F130" s="12"/>
       <c r="G130" s="12"/>
-      <c r="H130" s="21"/>
+      <c r="H130" s="21">
+        <v>1</v>
+      </c>
       <c r="I130" s="22" t="str">
         <f>IFERROR(INDEX($A$300:$A$311,MATCH(2,$E$300:$E$311,0)),"")</f>
         <v>Senegal</v>
@@ -10759,11 +10791,11 @@
       <c r="F138" s="12"/>
       <c r="G138" s="12"/>
       <c r="H138" s="25"/>
-      <c r="I138" s="69" t="s">
+      <c r="I138" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="J138" s="69"/>
-      <c r="K138" s="69"/>
+      <c r="J138" s="60"/>
+      <c r="K138" s="60"/>
       <c r="L138" s="12"/>
       <c r="M138" s="12"/>
       <c r="N138" s="12"/>
@@ -10795,7 +10827,7 @@
       <c r="G139" s="12"/>
       <c r="H139" s="15" t="str">
         <f>COUNTIF(H140:H155,1)&amp;"/8"</f>
-        <v>0/8</v>
+        <v>8/8</v>
       </c>
       <c r="I139" s="16" t="s">
         <v>18</v>
@@ -10831,7 +10863,9 @@
       <c r="E140" s="12"/>
       <c r="F140" s="12"/>
       <c r="G140" s="12"/>
-      <c r="H140" s="26"/>
+      <c r="H140" s="26">
+        <v>1</v>
+      </c>
       <c r="I140" s="27" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(1,$J$105:$J$136,0)),"")</f>
         <v>Brasil</v>
@@ -10908,7 +10942,9 @@
       <c r="E142" s="12"/>
       <c r="F142" s="12"/>
       <c r="G142" s="12"/>
-      <c r="H142" s="26"/>
+      <c r="H142" s="26">
+        <v>1</v>
+      </c>
       <c r="I142" s="27" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(3,$J$105:$J$136,0)),"")</f>
         <v>USA</v>
@@ -10985,7 +11021,9 @@
       <c r="E144" s="12"/>
       <c r="F144" s="12"/>
       <c r="G144" s="12"/>
-      <c r="H144" s="26"/>
+      <c r="H144" s="26">
+        <v>1</v>
+      </c>
       <c r="I144" s="27" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(5,$J$105:$J$136,0)),"")</f>
         <v>Belgia</v>
@@ -11023,7 +11061,9 @@
       <c r="E145" s="12"/>
       <c r="F145" s="12"/>
       <c r="G145" s="12"/>
-      <c r="H145" s="29"/>
+      <c r="H145" s="29">
+        <v>1</v>
+      </c>
       <c r="I145" s="30" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(6,$J$105:$J$136,0)),"")</f>
         <v>Spania</v>
@@ -11061,7 +11101,9 @@
       <c r="E146" s="12"/>
       <c r="F146" s="12"/>
       <c r="G146" s="12"/>
-      <c r="H146" s="26"/>
+      <c r="H146" s="26">
+        <v>1</v>
+      </c>
       <c r="I146" s="27" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(7,$J$105:$J$136,0)),"")</f>
         <v>Frankrike</v>
@@ -11099,7 +11141,9 @@
       <c r="E147" s="12"/>
       <c r="F147" s="12"/>
       <c r="G147" s="12"/>
-      <c r="H147" s="29"/>
+      <c r="H147" s="29">
+        <v>1</v>
+      </c>
       <c r="I147" s="30" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(8,$J$105:$J$136,0)),"")</f>
         <v>Argentina</v>
@@ -11137,7 +11181,9 @@
       <c r="E148" s="12"/>
       <c r="F148" s="12"/>
       <c r="G148" s="12"/>
-      <c r="H148" s="26"/>
+      <c r="H148" s="26">
+        <v>1</v>
+      </c>
       <c r="I148" s="27" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(9,$J$105:$J$136,0)),"")</f>
         <v>Portugal</v>
@@ -11292,7 +11338,9 @@
       <c r="E152" s="12"/>
       <c r="F152" s="12"/>
       <c r="G152" s="12"/>
-      <c r="H152" s="26"/>
+      <c r="H152" s="26">
+        <v>1</v>
+      </c>
       <c r="I152" s="27" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(13,$J$105:$J$136,0)),"")</f>
         <v>Norge</v>
@@ -11481,11 +11529,11 @@
       <c r="F157" s="12"/>
       <c r="G157" s="12"/>
       <c r="H157" s="32"/>
-      <c r="I157" s="64" t="s">
+      <c r="I157" s="53" t="s">
         <v>162</v>
       </c>
-      <c r="J157" s="64"/>
-      <c r="K157" s="64"/>
+      <c r="J157" s="53"/>
+      <c r="K157" s="53"/>
       <c r="L157" s="12"/>
       <c r="M157" s="12"/>
       <c r="N157" s="12"/>
@@ -11517,7 +11565,7 @@
       <c r="G158" s="12"/>
       <c r="H158" s="15" t="str">
         <f>COUNTIF(H159:H166,1)&amp;"/4"</f>
-        <v>0/4</v>
+        <v>4/4</v>
       </c>
       <c r="I158" s="16" t="s">
         <v>18</v>
@@ -11553,7 +11601,9 @@
       <c r="E159" s="12"/>
       <c r="F159" s="12"/>
       <c r="G159" s="12"/>
-      <c r="H159" s="33"/>
+      <c r="H159" s="33">
+        <v>1</v>
+      </c>
       <c r="I159" s="34" t="str">
         <f>IFERROR(INDEX($I$140:$I$155,MATCH(1,$J$140:$J$155,0)),"")</f>
         <v>Brasil</v>
@@ -11591,7 +11641,9 @@
       <c r="E160" s="12"/>
       <c r="F160" s="12"/>
       <c r="G160" s="12"/>
-      <c r="H160" s="36"/>
+      <c r="H160" s="36">
+        <v>1</v>
+      </c>
       <c r="I160" s="37" t="str">
         <f>IFERROR(INDEX($I$140:$I$155,MATCH(2,$J$140:$J$155,0)),"")</f>
         <v>Spania</v>
@@ -11629,7 +11681,9 @@
       <c r="E161" s="12"/>
       <c r="F161" s="12"/>
       <c r="G161" s="12"/>
-      <c r="H161" s="33"/>
+      <c r="H161" s="33">
+        <v>1</v>
+      </c>
       <c r="I161" s="34" t="str">
         <f>IFERROR(INDEX($I$140:$I$155,MATCH(3,$J$140:$J$155,0)),"")</f>
         <v>Frankrike</v>
@@ -11706,7 +11760,9 @@
       <c r="E163" s="12"/>
       <c r="F163" s="12"/>
       <c r="G163" s="12"/>
-      <c r="H163" s="33"/>
+      <c r="H163" s="33">
+        <v>1</v>
+      </c>
       <c r="I163" s="34" t="str">
         <f>IFERROR(INDEX($I$140:$I$155,MATCH(5,$J$140:$J$155,0)),"")</f>
         <v>Portugal</v>
@@ -11895,11 +11951,11 @@
       <c r="F168" s="12"/>
       <c r="G168" s="12"/>
       <c r="H168" s="39"/>
-      <c r="I168" s="65" t="s">
+      <c r="I168" s="54" t="s">
         <v>163</v>
       </c>
-      <c r="J168" s="65"/>
-      <c r="K168" s="65"/>
+      <c r="J168" s="54"/>
+      <c r="K168" s="54"/>
       <c r="L168" s="12"/>
       <c r="M168" s="12"/>
       <c r="N168" s="12"/>
@@ -11931,7 +11987,7 @@
       <c r="G169" s="12"/>
       <c r="H169" s="15" t="str">
         <f>COUNTIF(H170:H173,1)&amp;"/2"</f>
-        <v>0/2</v>
+        <v>2/2</v>
       </c>
       <c r="I169" s="16" t="s">
         <v>18</v>
@@ -12006,7 +12062,9 @@
       <c r="E171" s="12"/>
       <c r="F171" s="12"/>
       <c r="G171" s="12"/>
-      <c r="H171" s="43"/>
+      <c r="H171" s="43">
+        <v>1</v>
+      </c>
       <c r="I171" s="44" t="str">
         <f>IFERROR(INDEX($I$159:$I$166,MATCH(2,$J$159:$J$166,0)),"")</f>
         <v>Frankrike</v>
@@ -12044,7 +12102,9 @@
       <c r="E172" s="12"/>
       <c r="F172" s="12"/>
       <c r="G172" s="12"/>
-      <c r="H172" s="40"/>
+      <c r="H172" s="40">
+        <v>1</v>
+      </c>
       <c r="I172" s="41" t="str">
         <f>IFERROR(INDEX($I$159:$I$166,MATCH(3,$J$159:$J$166,0)),"")</f>
         <v>Portugal</v>
@@ -12155,11 +12215,11 @@
       <c r="F175" s="12"/>
       <c r="G175" s="12"/>
       <c r="H175" s="46"/>
-      <c r="I175" s="66" t="s">
+      <c r="I175" s="55" t="s">
         <v>164</v>
       </c>
-      <c r="J175" s="66"/>
-      <c r="K175" s="66"/>
+      <c r="J175" s="55"/>
+      <c r="K175" s="55"/>
       <c r="L175" s="12"/>
       <c r="M175" s="12"/>
       <c r="N175" s="12"/>
@@ -12191,7 +12251,7 @@
       <c r="G176" s="12"/>
       <c r="H176" s="15" t="str">
         <f>COUNTIF(H177:H178,1)&amp;"/1"</f>
-        <v>0/1</v>
+        <v>1/1</v>
       </c>
       <c r="I176" s="16" t="s">
         <v>18</v>
@@ -12227,7 +12287,9 @@
       <c r="E177" s="12"/>
       <c r="F177" s="12"/>
       <c r="G177" s="12"/>
-      <c r="H177" s="47"/>
+      <c r="H177" s="47">
+        <v>1</v>
+      </c>
       <c r="I177" s="48" t="str">
         <f>IFERROR(INDEX($I$170:$I$173,MATCH(1,$J$170:$J$173,0)),"")</f>
         <v>Frankrike</v>
@@ -17287,6 +17349,35 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="M1:U1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:K2"/>
+    <mergeCell ref="M2:U2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="M3:U3"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="M13:U13"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="M21:U21"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="M29:U29"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="M37:U37"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="A53:K53"/>
+    <mergeCell ref="M53:U53"/>
+    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="M61:U61"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="M77:U77"/>
+    <mergeCell ref="A85:K85"/>
+    <mergeCell ref="M85:U85"/>
     <mergeCell ref="I157:K157"/>
     <mergeCell ref="I168:K168"/>
     <mergeCell ref="I175:K175"/>
@@ -17295,35 +17386,6 @@
     <mergeCell ref="H101:K101"/>
     <mergeCell ref="I103:K103"/>
     <mergeCell ref="I138:K138"/>
-    <mergeCell ref="A69:K69"/>
-    <mergeCell ref="M69:U69"/>
-    <mergeCell ref="A77:K77"/>
-    <mergeCell ref="M77:U77"/>
-    <mergeCell ref="A85:K85"/>
-    <mergeCell ref="M85:U85"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="A53:K53"/>
-    <mergeCell ref="M53:U53"/>
-    <mergeCell ref="A61:K61"/>
-    <mergeCell ref="M61:U61"/>
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="M21:U21"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="M29:U29"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="M37:U37"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="M3:U3"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="M1:U1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:K2"/>
-    <mergeCell ref="M2:U2"/>
   </mergeCells>
   <conditionalFormatting sqref="H105:H136">
     <cfRule type="expression" dxfId="19" priority="2">
@@ -17436,17 +17498,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9cd4a677-7aee-4d17-8718-d38c4fab49a7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d4f56ad3-4be4-4368-a565-df4965c1e22f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100671046C6C42EE1449039E4EC9B42CCA1" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="80f13109c7168a888416f40688afc82a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9cd4a677-7aee-4d17-8718-d38c4fab49a7" xmlns:ns3="d4f56ad3-4be4-4368-a565-df4965c1e22f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="09d6a4af225531c3ac4b1ce681bc99f1" ns2:_="" ns3:_="">
     <xsd:import namespace="9cd4a677-7aee-4d17-8718-d38c4fab49a7"/>
@@ -17701,6 +17752,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9cd4a677-7aee-4d17-8718-d38c4fab49a7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d4f56ad3-4be4-4368-a565-df4965c1e22f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -17711,17 +17773,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5289171D-7414-480A-A6B0-4629BA2371E5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9cd4a677-7aee-4d17-8718-d38c4fab49a7"/>
-    <ds:schemaRef ds:uri="d4f56ad3-4be4-4368-a565-df4965c1e22f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E2AB9BB-D206-4B42-BC5A-546223F1217A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17740,6 +17791,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5289171D-7414-480A-A6B0-4629BA2371E5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9cd4a677-7aee-4d17-8718-d38c4fab49a7"/>
+    <ds:schemaRef ds:uri="d4f56ad3-4be4-4368-a565-df4965c1e22f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD46F970-DEC9-4AF4-95E8-BA2A2F98E5F2}">
   <ds:schemaRefs>
